--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N141_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N141_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.32511208964259</v>
+        <v>9.802830714566921</v>
       </c>
       <c r="D2" t="n">
-        <v>58.74407692834201</v>
+        <v>9.545912500855577</v>
       </c>
       <c r="E2" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F2" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.21513933379733</v>
+        <v>1.984960141742067</v>
       </c>
       <c r="D3" t="n">
-        <v>13.05707387610135</v>
+        <v>2.12177450486647</v>
       </c>
       <c r="E3" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F3" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.80193918494918</v>
+        <v>9.392815117554241</v>
       </c>
       <c r="D4" t="n">
-        <v>55.76142588402482</v>
+        <v>9.061231706154032</v>
       </c>
       <c r="E4" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F4" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.78482106232791</v>
+        <v>6.465033422628286</v>
       </c>
       <c r="D5" t="n">
-        <v>48.70043719348718</v>
+        <v>7.913821043941668</v>
       </c>
       <c r="E5" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F5" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.10706958602199</v>
+        <v>2.292398807728574</v>
       </c>
       <c r="D6" t="n">
-        <v>8.944271909999159</v>
+        <v>1.453444185374863</v>
       </c>
       <c r="E6" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F6" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.33412332224772</v>
+        <v>3.954295039865255</v>
       </c>
       <c r="D7" t="n">
-        <v>9.863252043261214</v>
+        <v>1.602778457029947</v>
       </c>
       <c r="E7" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F7" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.94413750027606</v>
+        <v>5.67842234379486</v>
       </c>
       <c r="D8" t="n">
-        <v>16.22498073958795</v>
+        <v>2.636559370183043</v>
       </c>
       <c r="E8" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F8" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72269742210282</v>
+        <v>5.804938331091709</v>
       </c>
       <c r="D9" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E9" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F9" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>60.18235070151033</v>
+        <v>9.77963198899543</v>
       </c>
       <c r="D10" t="n">
-        <v>27.96274510698123</v>
+        <v>4.543946079884451</v>
       </c>
       <c r="E10" t="n">
-        <v>17.70762656939759</v>
+        <v>2.877489317527109</v>
       </c>
       <c r="F10" t="n">
-        <v>19.75057244198629</v>
+        <v>3.209468021822772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
